--- a/excel/Sealant.xlsx
+++ b/excel/Sealant.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MKT_INTERNET04\Desktop\ข้อมูลทำราคาขาย\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritar/Desktop/SP684-SupplierInfo/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDD2664-4272-4EAF-BD78-7778947FF2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D26FC85-2AED-C741-BAB9-DCEBCDD76198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="23260" windowHeight="12460" tabRatio="808" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Price List" sheetId="18" r:id="rId1"/>
+    <sheet name="Ref." sheetId="19" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
   <si>
     <t>Internal Memo</t>
   </si>
@@ -231,8 +245,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -439,25 +453,25 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -468,15 +482,15 @@
     <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -497,16 +511,16 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -530,17 +544,17 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -549,43 +563,40 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -596,20 +607,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1110,18 +1124,18 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:O64"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="8" customWidth="1"/>
-    <col min="2" max="2" width="52.625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="48.125" customWidth="1"/>
-    <col min="4" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="7" max="9" width="15.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="52.59765625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="48.19921875" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" customWidth="1"/>
+    <col min="6" max="6" width="15.796875" customWidth="1"/>
+    <col min="7" max="9" width="15.796875" style="2" customWidth="1"/>
     <col min="10" max="10" width="5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="40.799999999999997" x14ac:dyDescent="1.05">
+    <row r="1" spans="2:15" ht="36" x14ac:dyDescent="0.4">
       <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1132,7 +1146,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C2" s="7" t="s">
         <v>29</v>
       </c>
@@ -1143,7 +1157,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C3" s="7" t="s">
         <v>30</v>
       </c>
@@ -1151,7 +1165,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="2:15" ht="23.4" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:15" ht="21" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1159,32 +1173,32 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="F7" s="56" t="s">
+    <row r="7" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="58"/>
-    </row>
-    <row r="8" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C8" s="59" t="s">
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
+    </row>
+    <row r="8" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="61"/>
+      <c r="E8" s="60"/>
       <c r="F8" s="21" t="s">
         <v>44</v>
       </c>
@@ -1200,13 +1214,13 @@
       <c r="K8" s="28"/>
       <c r="L8" s="28"/>
       <c r="M8" s="28"/>
-      <c r="N8" s="62"/>
-    </row>
-    <row r="9" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="N8" s="66"/>
+    </row>
+    <row r="9" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="60"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1216,20 +1230,20 @@
       <c r="F9" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="G9" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="64"/>
+      <c r="H9" s="62"/>
       <c r="I9" s="31" t="s">
         <v>26</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
-      <c r="N9" s="62"/>
-    </row>
-    <row r="10" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B10" s="65" t="s">
+      <c r="N9" s="66"/>
+    </row>
+    <row r="10" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="23" t="s">
@@ -1257,8 +1271,8 @@
       <c r="M10" s="29"/>
       <c r="N10" s="29"/>
     </row>
-    <row r="11" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B11" s="65" t="s">
+    <row r="11" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="23" t="s">
@@ -1286,8 +1300,8 @@
       <c r="M11" s="29"/>
       <c r="N11" s="29"/>
     </row>
-    <row r="12" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B12" s="65" t="s">
+    <row r="12" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="56" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="23" t="s">
@@ -1316,8 +1330,8 @@
       <c r="N12" s="30"/>
       <c r="O12" s="15"/>
     </row>
-    <row r="13" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B13" s="65" t="s">
+    <row r="13" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="56" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="23" t="s">
@@ -1346,8 +1360,8 @@
       <c r="N13" s="30"/>
       <c r="O13" s="15"/>
     </row>
-    <row r="14" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B14" s="65" t="s">
+    <row r="14" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="56" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="23" t="s">
@@ -1376,8 +1390,8 @@
       <c r="N14" s="30"/>
       <c r="O14" s="15"/>
     </row>
-    <row r="15" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B15" s="65" t="s">
+    <row r="15" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="56" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="23" t="s">
@@ -1406,7 +1420,7 @@
       <c r="N15" s="30"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" spans="2:15" ht="22.2" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="16" spans="2:15" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C16" s="23" t="s">
         <v>37</v>
       </c>
@@ -1422,7 +1436,7 @@
       <c r="N16" s="30"/>
       <c r="O16" s="15"/>
     </row>
-    <row r="17" spans="2:15" ht="22.2" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="17" spans="2:15" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="23" t="s">
         <v>39</v>
       </c>
@@ -1441,7 +1455,7 @@
       <c r="N17" s="30"/>
       <c r="O17" s="15"/>
     </row>
-    <row r="18" spans="2:15" ht="22.2" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="18" spans="2:15" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C18" s="23" t="s">
         <v>40</v>
       </c>
@@ -1457,8 +1471,8 @@
       <c r="N18" s="30"/>
       <c r="O18" s="15"/>
     </row>
-    <row r="19" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B19" s="66" t="s">
+    <row r="19" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="57" t="s">
         <v>61</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -1486,8 +1500,8 @@
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B20" s="65" t="s">
+    <row r="20" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="56" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="23" t="s">
@@ -1511,8 +1525,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B21" s="65" t="s">
+    <row r="21" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="23" t="s">
@@ -1536,8 +1550,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B22" s="65" t="s">
+    <row r="22" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="56" t="s">
         <v>58</v>
       </c>
       <c r="C22" s="23" t="s">
@@ -1561,7 +1575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="22.2" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="23" spans="2:15" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="43" t="s">
         <v>38</v>
       </c>
@@ -1583,8 +1597,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B24" s="65" t="s">
+    <row r="24" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="56" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -1609,8 +1623,8 @@
       </c>
       <c r="J24" s="40"/>
     </row>
-    <row r="25" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B25" s="65" t="s">
+    <row r="25" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="56" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="23" t="s">
@@ -1634,8 +1648,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B26" s="65" t="s">
+    <row r="26" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="56" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="23" t="s">
@@ -1659,8 +1673,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="27" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B27" s="65" t="s">
+    <row r="27" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="56" t="s">
         <v>63</v>
       </c>
       <c r="C27" s="23" t="s">
@@ -1684,8 +1698,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B28" s="65" t="s">
+    <row r="28" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="56" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="23" t="s">
@@ -1709,8 +1723,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="29" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B29" s="65" t="s">
+    <row r="29" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="56" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="39" t="s">
@@ -1734,8 +1748,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B30" s="65" t="s">
+    <row r="30" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="56" t="s">
         <v>65</v>
       </c>
       <c r="C30" s="39" t="s">
@@ -1760,7 +1774,7 @@
       </c>
       <c r="J30" s="45"/>
     </row>
-    <row r="31" spans="2:15" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="31" spans="2:15" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="25"/>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -1769,25 +1783,25 @@
       <c r="H31" s="27"/>
       <c r="I31" s="27"/>
     </row>
-    <row r="32" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="32" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="33"/>
       <c r="D32" s="34"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="56" t="s">
+      <c r="F32" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58"/>
-    </row>
-    <row r="33" spans="2:13" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C33" s="59" t="s">
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="65"/>
+    </row>
+    <row r="33" spans="2:13" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="61" t="s">
+      <c r="D33" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="61"/>
+      <c r="E33" s="60"/>
       <c r="F33" s="21" t="s">
         <v>44</v>
       </c>
@@ -1801,8 +1815,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C34" s="60"/>
+    <row r="34" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="59"/>
       <c r="D34" s="3" t="s">
         <v>33</v>
       </c>
@@ -1812,16 +1826,16 @@
       <c r="F34" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="63" t="s">
+      <c r="G34" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="H34" s="64"/>
+      <c r="H34" s="62"/>
       <c r="I34" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B35" s="65" t="s">
+    <row r="35" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="44" t="s">
@@ -1849,8 +1863,8 @@
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
     </row>
-    <row r="36" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B36" s="65" t="s">
+    <row r="36" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C36" s="44" t="s">
@@ -1877,8 +1891,8 @@
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
     </row>
-    <row r="37" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B37" s="65" t="s">
+    <row r="37" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C37" s="44" t="s">
@@ -1905,8 +1919,8 @@
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
     </row>
-    <row r="38" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B38" s="65" t="s">
+    <row r="38" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C38" s="44" t="s">
@@ -1933,8 +1947,8 @@
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
     </row>
-    <row r="39" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B39" s="65" t="s">
+    <row r="39" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C39" s="44" t="s">
@@ -1961,8 +1975,8 @@
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
     </row>
-    <row r="40" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B40" s="65" t="s">
+    <row r="40" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C40" s="44" t="s">
@@ -1989,7 +2003,7 @@
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
     </row>
-    <row r="41" spans="2:13" ht="6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="41" spans="2:13" ht="6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="22"/>
       <c r="D41" s="47"/>
       <c r="E41" s="47"/>
@@ -1998,8 +2012,8 @@
       <c r="H41" s="53"/>
       <c r="I41" s="53"/>
     </row>
-    <row r="42" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B42" s="65" t="s">
+    <row r="42" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C42" s="44" t="s">
@@ -2023,8 +2037,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B43" s="65" t="s">
+    <row r="43" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C43" s="44" t="s">
@@ -2048,8 +2062,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B44" s="65" t="s">
+    <row r="44" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C44" s="44" t="s">
@@ -2073,8 +2087,8 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B45" s="65" t="s">
+    <row r="45" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C45" s="44" t="s">
@@ -2098,8 +2112,8 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B46" s="65" t="s">
+    <row r="46" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C46" s="44" t="s">
@@ -2123,8 +2137,8 @@
         <v>382</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B47" s="65" t="s">
+    <row r="47" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="56" t="s">
         <v>66</v>
       </c>
       <c r="C47" s="44" t="s">
@@ -2148,7 +2162,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="48" spans="2:13" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="48" spans="2:13" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C48" s="12"/>
       <c r="D48" s="13"/>
       <c r="E48" s="13"/>
@@ -2157,25 +2171,25 @@
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
     </row>
-    <row r="49" spans="1:11" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
+    <row r="49" spans="1:11" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C49" s="12"/>
       <c r="D49" s="13"/>
       <c r="E49" s="13"/>
-      <c r="F49" s="56" t="s">
+      <c r="F49" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="58"/>
-    </row>
-    <row r="50" spans="1:11" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C50" s="59" t="s">
+      <c r="G49" s="64"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="65"/>
+    </row>
+    <row r="50" spans="1:11" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="61" t="s">
+      <c r="D50" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="61"/>
+      <c r="E50" s="60"/>
       <c r="F50" s="21" t="s">
         <v>44</v>
       </c>
@@ -2189,8 +2203,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="C51" s="60"/>
+    <row r="51" spans="1:11" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="59"/>
       <c r="D51" s="3" t="s">
         <v>33</v>
       </c>
@@ -2200,16 +2214,16 @@
       <c r="F51" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G51" s="63" t="s">
+      <c r="G51" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="H51" s="64"/>
+      <c r="H51" s="62"/>
       <c r="I51" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B52" s="65" t="s">
+    <row r="52" spans="1:11" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="56" t="s">
         <v>60</v>
       </c>
       <c r="C52" s="35" t="s">
@@ -2233,8 +2247,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B53" s="65" t="s">
+    <row r="53" spans="1:11" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="56" t="s">
         <v>60</v>
       </c>
       <c r="C53" s="35" t="s">
@@ -2258,8 +2272,8 @@
         <v>240</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="B54" s="66" t="s">
+    <row r="54" spans="1:11" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="57" t="s">
         <v>67</v>
       </c>
       <c r="C54" s="35" t="s">
@@ -2283,8 +2297,8 @@
         <v>370</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="21.6" thickTop="1" x14ac:dyDescent="0.6"/>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:11" ht="20" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="17"/>
       <c r="B56" s="17"/>
       <c r="C56" s="10"/>
@@ -2296,7 +2310,7 @@
       <c r="I56" s="18"/>
       <c r="K56" s="9"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="19"/>
       <c r="B57" s="19"/>
       <c r="C57" s="10"/>
@@ -2308,7 +2322,7 @@
       <c r="I57" s="18"/>
       <c r="K57" s="9"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="19"/>
       <c r="B58" s="19"/>
       <c r="C58" s="10"/>
@@ -2320,7 +2334,7 @@
       <c r="I58" s="18"/>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="20"/>
       <c r="B59" s="20"/>
       <c r="C59" s="10"/>
@@ -2332,7 +2346,7 @@
       <c r="I59" s="18"/>
       <c r="K59" s="9"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="19"/>
       <c r="C60" s="10"/>
@@ -2344,28 +2358,34 @@
       <c r="I60" s="18"/>
       <c r="K60" s="9"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="19"/>
       <c r="B61" s="19"/>
       <c r="K61" s="9"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="19"/>
       <c r="K62" s="9"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="19"/>
       <c r="B63" s="19"/>
       <c r="K63" s="9"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="K64" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="G9:H9"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="G34:H34"/>
@@ -2373,15 +2393,147 @@
     <mergeCell ref="C50:C51"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="G51:H51"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="G9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DCCCCB-F8C0-F84D-BC02-F5B1D89BC4C3}">
+  <dimension ref="A1:AF1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="40.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.19921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="28.19921875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/excel/Sealant.xlsx
+++ b/excel/Sealant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritar/Desktop/SP684-SupplierInfo/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D26FC85-2AED-C741-BAB9-DCEBCDD76198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3C28A3-A372-904D-8788-B5A43FFE7FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="23260" windowHeight="12460" tabRatio="808" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="23260" windowHeight="12460" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Price List" sheetId="18" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="125">
   <si>
     <t>Internal Memo</t>
   </si>
@@ -238,6 +238,177 @@
   </si>
   <si>
     <t>บริษัท เซ็งชัย ตกแต่ง จำกัด</t>
+  </si>
+  <si>
+    <t>S03020120200000600</t>
+  </si>
+  <si>
+    <t>S03020120500000600</t>
+  </si>
+  <si>
+    <t>S03020120300000600</t>
+  </si>
+  <si>
+    <t>S01010010100000300</t>
+  </si>
+  <si>
+    <t>S01010010200000300</t>
+  </si>
+  <si>
+    <t>S01010010300000300</t>
+  </si>
+  <si>
+    <t>S01010010500000300</t>
+  </si>
+  <si>
+    <t>S01010010600000300</t>
+  </si>
+  <si>
+    <t>S01010010700000300</t>
+  </si>
+  <si>
+    <t>S01010020100000300</t>
+  </si>
+  <si>
+    <t>S01010020200000300</t>
+  </si>
+  <si>
+    <t>S01010020300000300</t>
+  </si>
+  <si>
+    <t>S01010020700000300</t>
+  </si>
+  <si>
+    <t>S01010030100000300</t>
+  </si>
+  <si>
+    <t>S01010030200000300</t>
+  </si>
+  <si>
+    <t>S01010030300000300</t>
+  </si>
+  <si>
+    <t>S01010030400000300</t>
+  </si>
+  <si>
+    <t>S01010030500000300</t>
+  </si>
+  <si>
+    <t>S01010030600000300</t>
+  </si>
+  <si>
+    <t>S01010030700000300</t>
+  </si>
+  <si>
+    <t>S01010040100000300</t>
+  </si>
+  <si>
+    <t>S01010040200000300</t>
+  </si>
+  <si>
+    <t>S09050200200000460</t>
+  </si>
+  <si>
+    <t>S09050200700000460</t>
+  </si>
+  <si>
+    <t>S09050200300000460</t>
+  </si>
+  <si>
+    <t>S09050200900000460</t>
+  </si>
+  <si>
+    <t>S09050201200000460</t>
+  </si>
+  <si>
+    <t>S09050201300000460</t>
+  </si>
+  <si>
+    <t>S09050201400000460</t>
+  </si>
+  <si>
+    <t>S05050220200000470</t>
+  </si>
+  <si>
+    <t>S05050220700000470</t>
+  </si>
+  <si>
+    <t>S05050220300000470</t>
+  </si>
+  <si>
+    <t>S08050240200000460</t>
+  </si>
+  <si>
+    <t>S02050870200000300</t>
+  </si>
+  <si>
+    <t>S02050880900000300</t>
+  </si>
+  <si>
+    <t>S02050881000000300</t>
+  </si>
+  <si>
+    <t>S02050881100000300</t>
+  </si>
+  <si>
+    <t>S02050881200000300</t>
+  </si>
+  <si>
+    <t>S02050990200000300</t>
+  </si>
+  <si>
+    <t>S02040890300000290</t>
+  </si>
+  <si>
+    <t>S06060140700000300</t>
+  </si>
+  <si>
+    <t>S07050230200000430</t>
+  </si>
+  <si>
+    <t>S01010080200000300</t>
+  </si>
+  <si>
+    <t>S01010080300000300</t>
+  </si>
+  <si>
+    <t>S01010080500000300</t>
+  </si>
+  <si>
+    <t>S01010080200000500</t>
+  </si>
+  <si>
+    <t>S01010080300000500</t>
+  </si>
+  <si>
+    <t>S01010080500000500</t>
+  </si>
+  <si>
+    <t>S01010090100000300</t>
+  </si>
+  <si>
+    <t>S01010100300000300</t>
+  </si>
+  <si>
+    <t>S01010100300000600</t>
+  </si>
+  <si>
+    <t>S01010110200000600</t>
+  </si>
+  <si>
+    <t>S01010110300000600</t>
+  </si>
+  <si>
+    <t>S01010110500000600</t>
+  </si>
+  <si>
+    <t>S00070150000000000</t>
+  </si>
+  <si>
+    <t>S09070160800000000</t>
+  </si>
+  <si>
+    <t>S00070170000000000</t>
   </si>
 </sst>
 </file>
@@ -2402,25 +2573,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95DCCCCB-F8C0-F84D-BC02-F5B1D89BC4C3}">
-  <dimension ref="A1:AF1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="21.19921875" customWidth="1"/>
     <col min="7" max="7" width="22.796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="44.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.796875" customWidth="1"/>
     <col min="12" max="12" width="28" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="29.59765625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="40.59765625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="20.19921875" customWidth="1"/>
     <col min="18" max="18" width="27" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="27.796875" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="27" bestFit="1" customWidth="1"/>
@@ -2430,9 +2598,7 @@
     <col min="25" max="25" width="28.19921875" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="27.3984375" bestFit="1" customWidth="1"/>
     <col min="28" max="29" width="28.19921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="20.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -2533,6 +2699,227 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P2" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>109</v>
+      </c>
+      <c r="R2" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" t="s">
+        <v>113</v>
+      </c>
+      <c r="T2" t="s">
+        <v>116</v>
+      </c>
+      <c r="U2" t="s">
+        <v>117</v>
+      </c>
+      <c r="V2" t="s">
+        <v>118</v>
+      </c>
+      <c r="W2" t="s">
+        <v>119</v>
+      </c>
+      <c r="X2" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" t="s">
+        <v>111</v>
+      </c>
+      <c r="S3" t="s">
+        <v>114</v>
+      </c>
+      <c r="W3" t="s">
+        <v>120</v>
+      </c>
+      <c r="X3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" t="s">
+        <v>104</v>
+      </c>
+      <c r="R4" t="s">
+        <v>112</v>
+      </c>
+      <c r="S4" t="s">
+        <v>115</v>
+      </c>
+      <c r="W4" t="s">
+        <v>121</v>
+      </c>
+      <c r="X4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/Sealant.xlsx
+++ b/excel/Sealant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritar/Desktop/SP684-SupplierInfo/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3C28A3-A372-904D-8788-B5A43FFE7FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5043C917-6D7E-594F-ADEF-0EA194566446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="23260" windowHeight="12460" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -769,6 +769,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,23 +787,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1355,21 +1355,21 @@
       </c>
     </row>
     <row r="7" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F7" s="63" t="s">
+      <c r="F7" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="65"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="60"/>
     </row>
     <row r="8" spans="2:15" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="60"/>
+      <c r="E8" s="63"/>
       <c r="F8" s="21" t="s">
         <v>44</v>
       </c>
@@ -1385,13 +1385,13 @@
       <c r="K8" s="28"/>
       <c r="L8" s="28"/>
       <c r="M8" s="28"/>
-      <c r="N8" s="66"/>
+      <c r="N8" s="64"/>
     </row>
     <row r="9" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="59"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1401,17 +1401,17 @@
       <c r="F9" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="62"/>
+      <c r="H9" s="66"/>
       <c r="I9" s="31" t="s">
         <v>26</v>
       </c>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
-      <c r="N9" s="66"/>
+      <c r="N9" s="64"/>
     </row>
     <row r="10" spans="2:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56" t="s">
@@ -1958,21 +1958,21 @@
       <c r="C32" s="33"/>
       <c r="D32" s="34"/>
       <c r="E32" s="34"/>
-      <c r="F32" s="63" t="s">
+      <c r="F32" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="65"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="60"/>
     </row>
     <row r="33" spans="2:13" ht="23.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="60"/>
+      <c r="E33" s="63"/>
       <c r="F33" s="21" t="s">
         <v>44</v>
       </c>
@@ -1987,7 +1987,7 @@
       </c>
     </row>
     <row r="34" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="59"/>
+      <c r="C34" s="62"/>
       <c r="D34" s="3" t="s">
         <v>33</v>
       </c>
@@ -1997,10 +1997,10 @@
       <c r="F34" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="H34" s="62"/>
+      <c r="H34" s="66"/>
       <c r="I34" s="31" t="s">
         <v>26</v>
       </c>
@@ -2346,21 +2346,21 @@
       <c r="C49" s="12"/>
       <c r="D49" s="13"/>
       <c r="E49" s="13"/>
-      <c r="F49" s="63" t="s">
+      <c r="F49" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="G49" s="64"/>
-      <c r="H49" s="64"/>
-      <c r="I49" s="65"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="60"/>
     </row>
     <row r="50" spans="1:11" ht="22" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="60" t="s">
+      <c r="D50" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="60"/>
+      <c r="E50" s="63"/>
       <c r="F50" s="21" t="s">
         <v>44</v>
       </c>
@@ -2375,7 +2375,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C51" s="59"/>
+      <c r="C51" s="62"/>
       <c r="D51" s="3" t="s">
         <v>33</v>
       </c>
@@ -2385,10 +2385,10 @@
       <c r="F51" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G51" s="61" t="s">
+      <c r="G51" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="H51" s="62"/>
+      <c r="H51" s="66"/>
       <c r="I51" s="31" t="s">
         <v>26</v>
       </c>
@@ -2551,12 +2551,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="G9:H9"/>
     <mergeCell ref="C33:C34"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="G34:H34"/>
@@ -2564,6 +2558,12 @@
     <mergeCell ref="C50:C51"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="G51:H51"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="G9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
